--- a/Source data/Fig.3F.xlsx
+++ b/Source data/Fig.3F.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GITHUB\HGT_and_fitness\Source data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\HGT_and_fitness\Source data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9460AFE1-48DF-469E-B252-93BB77998123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{063E7C8B-A9AD-4498-8799-A6293A6EC572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14055" yWindow="4275" windowWidth="16140" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="19200" windowHeight="10050" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="top" sheetId="1" r:id="rId1"/>
@@ -199,7 +199,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -214,11 +214,6 @@
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -562,9 +557,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U37"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -629,7 +624,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -694,7 +689,7 @@
         <v>80430</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -759,7 +754,7 @@
         <v>69180</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -824,7 +819,7 @@
         <v>88089</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -889,7 +884,7 @@
         <v>89919</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -954,7 +949,7 @@
         <v>103053</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -1019,7 +1014,7 @@
         <v>104592</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -1084,7 +1079,7 @@
         <v>117449</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -1149,7 +1144,7 @@
         <v>109324</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -1214,7 +1209,7 @@
         <v>108073</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1279,7 +1274,7 @@
         <v>70599</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>31</v>
       </c>
@@ -1344,7 +1339,7 @@
         <v>88803</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -1409,7 +1404,7 @@
         <v>77068</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -1474,7 +1469,7 @@
         <v>88638</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -1539,7 +1534,7 @@
         <v>84087</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -1604,7 +1599,7 @@
         <v>76857</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>36</v>
       </c>
@@ -1669,7 +1664,7 @@
         <v>75720</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -1734,7 +1729,7 @@
         <v>78914</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -1799,7 +1794,7 @@
         <v>77108</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>39</v>
       </c>
@@ -1864,7 +1859,7 @@
         <v>79750</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -1929,7 +1924,7 @@
         <v>83961</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>41</v>
       </c>
@@ -1994,7 +1989,7 @@
         <v>86626</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>42</v>
       </c>
@@ -2059,7 +2054,7 @@
         <v>84845</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>43</v>
       </c>
@@ -2124,7 +2119,7 @@
         <v>78267</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>44</v>
       </c>
@@ -2189,7 +2184,7 @@
         <v>76669</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>45</v>
       </c>
@@ -2254,7 +2249,7 @@
         <v>77590</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>46</v>
       </c>
@@ -2319,7 +2314,7 @@
         <v>80137</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>47</v>
       </c>
@@ -2384,7 +2379,7 @@
         <v>87790</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>48</v>
       </c>
@@ -2449,7 +2444,7 @@
         <v>85560</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>49</v>
       </c>
@@ -2514,7 +2509,7 @@
         <v>79143</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>50</v>
       </c>
@@ -2579,7 +2574,7 @@
         <v>80878</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>51</v>
       </c>
@@ -2644,7 +2639,7 @@
         <v>78199</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>52</v>
       </c>
@@ -2709,7 +2704,7 @@
         <v>160416</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>53</v>
       </c>
@@ -2774,7 +2769,7 @@
         <v>109913</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>54</v>
       </c>
@@ -2839,7 +2834,7 @@
         <v>96853</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>55</v>
       </c>
@@ -2904,7 +2899,7 @@
         <v>83216</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>56</v>
       </c>
@@ -2979,9 +2974,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:T7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -3040,7 +3035,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -3102,7 +3097,7 @@
         <v>49.079656965487551</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -3164,7 +3159,7 @@
         <v>48.061606299545929</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>30</v>
       </c>
@@ -3226,7 +3221,7 @@
         <v>90.238931495161779</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -3288,7 +3283,7 @@
         <v>30.973921560908579</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>39</v>
       </c>
@@ -3350,7 +3345,7 @@
         <v>27.63045517780424</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>54</v>
       </c>
@@ -3422,9 +3417,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:T7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>2</v>
       </c>
@@ -3483,12 +3478,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>22</v>
       </c>
       <c r="B2">
-        <v>6.6890988999999998E-2</v>
+        <v>4.6285879599999899E-2</v>
       </c>
       <c r="C2">
         <v>465.8739025077889</v>
@@ -3545,12 +3540,12 @@
         <v>49.079656965487551</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3">
-        <v>7.2596068999999999E-2</v>
+        <v>4.8998357099999897E-2</v>
       </c>
       <c r="C3">
         <v>824.0181219406079</v>
@@ -3607,12 +3602,12 @@
         <v>48.061606299545929</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>30</v>
       </c>
       <c r="B4">
-        <v>5.3066308999999999E-2</v>
+        <v>4.3596416699999897E-2</v>
       </c>
       <c r="C4">
         <v>303.56171080620601</v>
@@ -3669,12 +3664,12 @@
         <v>90.238931495161779</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>33</v>
       </c>
       <c r="B5">
-        <v>6.3096339000000001E-2</v>
+        <v>4.4702981899999897E-2</v>
       </c>
       <c r="C5">
         <v>320.21913951768539</v>
@@ -3731,12 +3726,12 @@
         <v>30.973921560908579</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>39</v>
       </c>
       <c r="B6">
-        <v>5.1202235999999998E-2</v>
+        <v>4.4230087099999899E-2</v>
       </c>
       <c r="C6">
         <v>260.37239988229209</v>
@@ -3793,12 +3788,12 @@
         <v>27.63045517780424</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>54</v>
       </c>
       <c r="B7">
-        <v>5.7059387000000003E-2</v>
+        <v>4.43015885999999E-2</v>
       </c>
       <c r="C7">
         <v>224.55386155337339</v>
